--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1263,6 +1263,262 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110866418</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105852</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vårviks-Backa 33 (2), Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>341320</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6570044</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>OD-Ben-0349</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Claes Kannesten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110866489</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105852</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vårviks-Backa 33 (3), Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>341293</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6570125</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>OD-Ben-0350</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Claes Kannesten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>110866418</v>
       </c>
       <c r="B7" t="n">
-        <v>105852</v>
+        <v>105859</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>110866489</v>
       </c>
       <c r="B8" t="n">
-        <v>105852</v>
+        <v>105859</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>110866418</v>
       </c>
       <c r="B7" t="n">
-        <v>105859</v>
+        <v>105864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>110866489</v>
       </c>
       <c r="B8" t="n">
-        <v>105859</v>
+        <v>105864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>110866418</v>
       </c>
       <c r="B7" t="n">
-        <v>105864</v>
+        <v>105894</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>110866489</v>
       </c>
       <c r="B8" t="n">
-        <v>105864</v>
+        <v>105894</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110866418</v>
+        <v>110866489</v>
       </c>
       <c r="B7" t="n">
         <v>105894</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1317,14 +1317,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vårviks-Backa 33 (2), Dls</t>
+          <t>Vårviks-Backa 33 (3), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341320</v>
+        <v>341293</v>
       </c>
       <c r="R7" t="n">
-        <v>6570044</v>
+        <v>6570125</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>OD-Ben-0349</t>
+          <t>OD-Ben-0350</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110866489</v>
+        <v>110866418</v>
       </c>
       <c r="B8" t="n">
         <v>105894</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,14 +1445,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vårviks-Backa 33 (3), Dls</t>
+          <t>Vårviks-Backa 33 (2), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341293</v>
+        <v>341320</v>
       </c>
       <c r="R8" t="n">
-        <v>6570125</v>
+        <v>6570044</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>OD-Ben-0350</t>
+          <t>OD-Ben-0349</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110866489</v>
+        <v>110866418</v>
       </c>
       <c r="B7" t="n">
-        <v>105894</v>
+        <v>105908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1317,14 +1317,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vårviks-Backa 33 (3), Dls</t>
+          <t>Vårviks-Backa 33 (2), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341293</v>
+        <v>341320</v>
       </c>
       <c r="R7" t="n">
-        <v>6570125</v>
+        <v>6570044</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>OD-Ben-0350</t>
+          <t>OD-Ben-0349</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1393,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110866418</v>
+        <v>110866489</v>
       </c>
       <c r="B8" t="n">
-        <v>105894</v>
+        <v>105908</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,14 +1445,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vårviks-Backa 33 (2), Dls</t>
+          <t>Vårviks-Backa 33 (3), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341320</v>
+        <v>341293</v>
       </c>
       <c r="R8" t="n">
-        <v>6570044</v>
+        <v>6570125</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>OD-Ben-0349</t>
+          <t>OD-Ben-0350</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110866418</v>
+        <v>110866489</v>
       </c>
       <c r="B7" t="n">
         <v>105908</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1317,14 +1317,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vårviks-Backa 33 (2), Dls</t>
+          <t>Vårviks-Backa 33 (3), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341320</v>
+        <v>341293</v>
       </c>
       <c r="R7" t="n">
-        <v>6570044</v>
+        <v>6570125</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>OD-Ben-0349</t>
+          <t>OD-Ben-0350</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110866489</v>
+        <v>110866418</v>
       </c>
       <c r="B8" t="n">
         <v>105908</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,14 +1445,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vårviks-Backa 33 (3), Dls</t>
+          <t>Vårviks-Backa 33 (2), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341293</v>
+        <v>341320</v>
       </c>
       <c r="R8" t="n">
-        <v>6570125</v>
+        <v>6570044</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>OD-Ben-0350</t>
+          <t>OD-Ben-0349</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110866489</v>
+        <v>110866418</v>
       </c>
       <c r="B7" t="n">
         <v>105908</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1317,14 +1317,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vårviks-Backa 33 (3), Dls</t>
+          <t>Vårviks-Backa 33 (2), Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341293</v>
+        <v>341320</v>
       </c>
       <c r="R7" t="n">
-        <v>6570125</v>
+        <v>6570044</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>OD-Ben-0350</t>
+          <t>OD-Ben-0349</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1393,7 +1393,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110866418</v>
+        <v>110866489</v>
       </c>
       <c r="B8" t="n">
         <v>105908</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1445,14 +1445,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vårviks-Backa 33 (2), Dls</t>
+          <t>Vårviks-Backa 33 (3), Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341320</v>
+        <v>341293</v>
       </c>
       <c r="R8" t="n">
-        <v>6570044</v>
+        <v>6570125</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>OD-Ben-0349</t>
+          <t>OD-Ben-0350</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68546-2020 artfynd.xlsx
+++ b/artfynd/A 68546-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1263,262 +1263,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>110866489</v>
-      </c>
-      <c r="B7" t="n">
-        <v>106168</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>245</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Campanula cervicaria</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Vårviks-Backa 33 (3), Dls</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>341293</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6570125</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Bengtsfors</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Vårvik</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>OD-Ben-0350</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Claes Kannesten</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>110866418</v>
-      </c>
-      <c r="B8" t="n">
-        <v>106168</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>245</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Campanula cervicaria</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Vårviks-Backa 33 (2), Dls</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>341320</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6570044</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Bengtsfors</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Vårvik</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>OD-Ben-0349</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Claes Kannesten</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
